--- a/assets/data/excel/abilities.xlsx
+++ b/assets/data/excel/abilities.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,6 +5786,546 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TANK_HIDDEN_01</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>不灭甲</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>厚甲与再生融合产生的不灭甲：永久减少8%受到的伤害，每回合回复3%最大生命值</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>damage_reduce_percent</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TANK_HIDDEN_02</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>钢铁意志</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>挑衅与守护之盾融合产生的钢铁意志：嘲讽状态下替队友承伤时30%概率反弹伤害</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>on_damage_redirect</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>reflect_damage</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TANK_HIDDEN_03</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>铁根之体</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>扎根与钢铁意志融合产生的铁根之体：每损失10%生命值获得3%减伤</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>damage_reduce_per_missing_hp</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="b">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>10</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DPS_HIDDEN_01</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>暴击穿透</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>暴击强化与穿甲融合产生的暴击穿透：暴击时无视目标20%减伤</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>enemy_single</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>on_crit</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ignore_damage_reduce</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DPS_HIDDEN_02</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>暴风连击</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>暴击伤害与快速打击融合产生的暴风连击：暴击时50%概率追加一次普攻</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>enemy_single</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>on_crit</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>extra_attack</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DPS_HIDDEN_03</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>猎杀本能</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>狩猎本能与处决融合产生的猎杀本能：对生命低于50%的敌人伤害提升30%且暴击率提升15%</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>damage_boost_vs_low_hp</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DPS_HIDDEN_04</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>烈焰之心</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>燃烧意志与攻击强化融合产生的烈焰之心：永久提升10%攻击力</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>buff</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>atk_boost_percent</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SUP_HIDDEN_01</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>战歌</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>持续恢复与攻击鼓舞融合产生的战歌：治疗队友时为其提升8%攻击力持续3回合</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ally_single</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>on_heal</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>atk_boost_percent</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SUP_HIDDEN_02</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>压制</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>弱化与虚弱融合产生的压制：攻击时同时降低目标10%攻击力和10%速度持续2回合</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>enemy_single</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>on_hit</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>atk_reduce_percent</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>2</v>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SUP_HIDDEN_03</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>净化治愈</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>净化之水与治愈之心融合产生的净化治愈：每回合为生命最低队友回复15%攻击力生命并清除1个debuff</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>ally_lowest_hp</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>turn_start</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>heal_atk_percent</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>hidden</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/assets/data/excel/abilities.xlsx
+++ b/assets/data/excel/abilities.xlsx
@@ -2505,7 +2505,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>永久提升自身攻击力15%</t>
+          <t>所有元素技能伤害提升15%，与自身元素属性无关的通用元素增伤</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>atk_boost_percent</t>
+          <t>element_damage_boost</t>
         </is>
       </c>
       <c r="H39" t="n">
